--- a/results/tables/03_env_driven_taxa_clusters/table3_lda_axes_summary.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table3_lda_axes_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,9 +452,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>88.41034717281686</v>
       </c>
       <c r="C2" t="n">
+        <v>88.41034717281686</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>LD2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11.58965282718315</v>
+      </c>
+      <c r="C3" t="n">
         <v>100</v>
       </c>
     </row>
